--- a/attendance_report.xlsx
+++ b/attendance_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PoWeR\OneDrive\سطح المكتب\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PoWeR\OneDrive\Documents\GitHub\dawaa-pharmacy-2027-executive-dashboard-upgrade\fixwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F0FC39-5E37-40BE-8564-933BD70F46D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F2209B-7EDA-4977-8A88-37E7112D20CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الفرع الشامي" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="76">
   <si>
     <t>د/ شيماء</t>
   </si>
@@ -277,6 +277,10 @@
   <si>
     <t>9 AM → 5PM
 (8h)</t>
+  </si>
+  <si>
+    <t>6 PM → 4 AM
+(12h)</t>
   </si>
 </sst>
 </file>
@@ -372,7 +376,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,6 +422,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -509,13 +519,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,17 +534,30 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -859,30 +875,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -929,7 +945,7 @@
       <c r="F4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -952,7 +968,7 @@
       <c r="E5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -969,7 +985,7 @@
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -998,7 +1014,7 @@
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -1007,7 +1023,7 @@
       <c r="F7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="8" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="6" t="s">
@@ -1024,7 +1040,7 @@
       <c r="C8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -1033,7 +1049,7 @@
       <c r="F8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="8" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -1050,7 +1066,7 @@
       <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -1059,10 +1075,10 @@
       <c r="F9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="9" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1079,7 +1095,7 @@
       <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="5" t="s">
@@ -1093,10 +1109,10 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="37.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
@@ -1117,28 +1133,28 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:9" ht="35.4" x14ac:dyDescent="0.6">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1147,22 +1163,22 @@
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" s="12" t="s">
+      <c r="F15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="9" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1173,22 +1189,22 @@
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="15" t="s">
+      <c r="F16" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="G16" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1199,22 +1215,22 @@
       <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="15" t="s">
+      <c r="C17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="15" t="s">
+      <c r="F17" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="G17" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1225,22 +1241,22 @@
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="C18" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="15" t="s">
+      <c r="F18" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="G18" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1251,22 +1267,22 @@
       <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="15" t="s">
+      <c r="C19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="15" t="s">
+      <c r="F19" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="G19" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1277,22 +1293,22 @@
       <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="15" t="s">
+      <c r="F20" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="G20" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1303,22 +1319,22 @@
       <c r="B21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="C21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="F21" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1329,22 +1345,22 @@
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="C22" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="15" t="s">
+      <c r="F22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H22" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1371,33 +1387,34 @@
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="35.4" x14ac:dyDescent="0.6">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1442,7 +1459,7 @@
       <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -1466,10 +1483,10 @@
       <c r="D5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -1496,14 +1513,14 @@
       <c r="E6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="5"/>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1523,7 +1540,7 @@
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G7" s="6" t="s">
@@ -1544,13 +1561,13 @@
       <c r="C8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G8" s="5" t="s">
@@ -1568,7 +1585,7 @@
       <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1577,7 +1594,7 @@
       <c r="E9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1604,42 +1621,42 @@
       <c r="E10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="13"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
     </row>
     <row r="13" spans="1:9" ht="35.4" x14ac:dyDescent="0.6">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1648,25 +1665,25 @@
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="H14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1677,25 +1694,25 @@
       <c r="B15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="15" t="s">
+      <c r="H15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1706,25 +1723,25 @@
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="15" t="s">
+      <c r="C16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I16" s="15" t="s">
+      <c r="H16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1735,25 +1752,25 @@
       <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="C17" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="15" t="s">
+      <c r="H17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1764,25 +1781,25 @@
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="C18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I18" s="15" t="s">
+      <c r="H18" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1793,25 +1810,25 @@
       <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="15" t="s">
+      <c r="C19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H19" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="15" t="s">
+      <c r="H19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1822,25 +1839,25 @@
       <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="H20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1851,25 +1868,25 @@
       <c r="B21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="H21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>61</v>
       </c>
     </row>
